--- a/outputs/step_disease_logistic/fpca_cumulative_variance.xlsx
+++ b/outputs/step_disease_logistic/fpca_cumulative_variance.xlsx
@@ -399,7 +399,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.8430926853113537</v>
+        <v>0.8459623704317526</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
@@ -410,7 +410,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.9476592195165879</v>
+        <v>0.9480655847461833</v>
       </c>
       <c r="C3" t="b">
         <v>0</v>
@@ -421,7 +421,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.9736354937950013</v>
+        <v>0.9738125163407039</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -432,7 +432,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.9845598083031647</v>
+        <v>0.9847483146576784</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
@@ -443,7 +443,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.990904611410159</v>
+        <v>0.9909827158893617</v>
       </c>
       <c r="C6" t="b">
         <v>0</v>
@@ -454,7 +454,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.9941565475823065</v>
+        <v>0.9942111171759379</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
@@ -465,7 +465,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.995994718329661</v>
+        <v>0.9960358039888511</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -476,7 +476,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.9972808379465026</v>
+        <v>0.9973181838790771</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
@@ -487,7 +487,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.9980002957345666</v>
+        <v>0.9979928437972452</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
@@ -498,7 +498,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.9985262375693498</v>
+        <v>0.9985080571198647</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.9988417495790008</v>
+        <v>0.9988477088801961</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.9990751598682017</v>
+        <v>0.9990769312901332</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
@@ -531,7 +531,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.9992515397838249</v>
+        <v>0.9992522139992801</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
@@ -542,7 +542,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.9993772676033975</v>
+        <v>0.9993784929734145</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
@@ -553,7 +553,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.9994653977703892</v>
+        <v>0.9994663814075618</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
@@ -564,7 +564,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.9995311912049877</v>
+        <v>0.9995303604695225</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.9995806864619077</v>
+        <v>0.999581799960094</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
@@ -586,7 +586,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.99961643539318</v>
+        <v>0.9996183888569488</v>
       </c>
       <c r="C19" t="b">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.9996498626377061</v>
+        <v>0.9996520142567473</v>
       </c>
       <c r="C20" t="b">
         <v>0</v>
@@ -608,7 +608,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.9996736713210005</v>
+        <v>0.999676006128891</v>
       </c>
       <c r="C21" t="b">
         <v>0</v>
